--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -52,556 +52,571 @@
     <t>valuation_flag</t>
   </si>
   <si>
+    <t>AWL</t>
+  </si>
+  <si>
+    <t>BRITANNIA</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO</t>
+  </si>
+  <si>
+    <t>GODREJCP</t>
+  </si>
+  <si>
+    <t>AMBUJACEM</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>INDIGO</t>
+  </si>
+  <si>
+    <t>BPCL</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>ADANIENT</t>
+  </si>
+  <si>
+    <t>ICICIPRULI</t>
+  </si>
+  <si>
+    <t>PFC</t>
+  </si>
+  <si>
+    <t>JIOFIN</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>POLYCAB</t>
+  </si>
+  <si>
+    <t>ADANIPORTS</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>BOSCHLTD</t>
+  </si>
+  <si>
+    <t>POLICYBZR</t>
+  </si>
+  <si>
     <t>HINDUNILVR</t>
   </si>
   <si>
-    <t>ICICIPRULI</t>
+    <t>LODHA</t>
+  </si>
+  <si>
+    <t>MANKIND</t>
+  </si>
+  <si>
+    <t>DIVISLAB</t>
   </si>
   <si>
     <t>ABB</t>
   </si>
   <si>
+    <t>PERSISTENT</t>
+  </si>
+  <si>
+    <t>ZOMATO</t>
+  </si>
+  <si>
+    <t>TCS</t>
+  </si>
+  <si>
+    <t>PAYTM</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>KOTAKBANK</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>TATAELXSI</t>
+  </si>
+  <si>
+    <t>TATACHEM</t>
+  </si>
+  <si>
+    <t>TATACOMM</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>PAGEIND</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>COLPAL</t>
+  </si>
+  <si>
+    <t>ASIANPAINT</t>
+  </si>
+  <si>
+    <t>IRCTC</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>ONGC</t>
+  </si>
+  <si>
+    <t>VEDL</t>
+  </si>
+  <si>
+    <t>MARUTI</t>
+  </si>
+  <si>
+    <t>BHARTIARTL</t>
+  </si>
+  <si>
+    <t>INTERGLOBE</t>
+  </si>
+  <si>
+    <t>LTIM</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>TATAMOTORS</t>
+  </si>
+  <si>
+    <t>ICICIBANK</t>
+  </si>
+  <si>
+    <t>PIDILITIND</t>
+  </si>
+  <si>
+    <t>DLF</t>
+  </si>
+  <si>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>TRENT</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>INFY</t>
+  </si>
+  <si>
+    <t>HEROMOTOCO</t>
+  </si>
+  <si>
+    <t>CHOLAFIN</t>
+  </si>
+  <si>
+    <t>RECLTD</t>
+  </si>
+  <si>
     <t>GAIL</t>
   </si>
   <si>
+    <t>M_M</t>
+  </si>
+  <si>
+    <t>MOTHERSON</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>JSWSTEEL</t>
+  </si>
+  <si>
+    <t>VBL</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>SRF</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>GRASIM</t>
+  </si>
+  <si>
+    <t>ICICIGI</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>HCLTECH</t>
+  </si>
+  <si>
+    <t>DRREDDY</t>
+  </si>
+  <si>
+    <t>SAIL</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
     <t>CANBK</t>
   </si>
   <si>
-    <t>RECLTD</t>
-  </si>
-  <si>
-    <t>SBIN</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>AMBUJACEM</t>
-  </si>
-  <si>
-    <t>PAYTM</t>
-  </si>
-  <si>
-    <t>HCLTECH</t>
-  </si>
-  <si>
-    <t>ADANIENT</t>
+    <t>IOC</t>
+  </si>
+  <si>
+    <t>TATAINVEST</t>
   </si>
   <si>
     <t>HDFCLIFE</t>
   </si>
   <si>
-    <t>CHOLAFIN</t>
-  </si>
-  <si>
-    <t>PAGEIND</t>
-  </si>
-  <si>
-    <t>TATAELXSI</t>
-  </si>
-  <si>
-    <t>SRF</t>
-  </si>
-  <si>
-    <t>BRITANNIA</t>
-  </si>
-  <si>
-    <t>TATAMOTORS</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>MANKIND</t>
-  </si>
-  <si>
-    <t>IRCTC</t>
-  </si>
-  <si>
-    <t>JSWSTEEL</t>
-  </si>
-  <si>
-    <t>KOTAKBANK</t>
-  </si>
-  <si>
-    <t>GRASIM</t>
-  </si>
-  <si>
-    <t>HEROMOTOCO</t>
-  </si>
-  <si>
-    <t>TATAINVEST</t>
-  </si>
-  <si>
-    <t>DRREDDY</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>INTERGLOBE</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP</t>
-  </si>
-  <si>
-    <t>BAJFINANCE</t>
-  </si>
-  <si>
     <t>MUTHOOTFIN</t>
   </si>
   <si>
     <t>IDFCFIRSTB</t>
   </si>
   <si>
-    <t>PIDILITIND</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>TATACOMM</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>POLYCAB</t>
-  </si>
-  <si>
-    <t>POLICYBZR</t>
-  </si>
-  <si>
-    <t>PFC</t>
-  </si>
-  <si>
-    <t>LTIM</t>
-  </si>
-  <si>
-    <t>DIVISLAB</t>
-  </si>
-  <si>
-    <t>MOTHERSON</t>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>INDUSINDBK</t>
+  </si>
+  <si>
+    <t>VARUNBEV</t>
+  </si>
+  <si>
+    <t>MAXHEALTH</t>
   </si>
   <si>
     <t>RELIANCE</t>
   </si>
   <si>
-    <t>M_M</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>TATASTEEL</t>
-  </si>
-  <si>
-    <t>ZOMATO</t>
-  </si>
-  <si>
-    <t>DLF</t>
-  </si>
-  <si>
-    <t>VARUNBEV</t>
-  </si>
-  <si>
-    <t>PERSISTENT</t>
-  </si>
-  <si>
-    <t>ICICIBANK</t>
-  </si>
-  <si>
-    <t>SUNPHARMA</t>
-  </si>
-  <si>
-    <t>GODREJCP</t>
-  </si>
-  <si>
-    <t>SAIL</t>
-  </si>
-  <si>
-    <t>VEDL</t>
-  </si>
-  <si>
-    <t>ONGC</t>
-  </si>
-  <si>
-    <t>TATACHEM</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO</t>
-  </si>
-  <si>
-    <t>COLPAL</t>
-  </si>
-  <si>
-    <t>BHARTIARTL</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>AWL</t>
-  </si>
-  <si>
-    <t>BOSCHLTD</t>
-  </si>
-  <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>JIOFIN</t>
-  </si>
-  <si>
-    <t>LODHA</t>
-  </si>
-  <si>
-    <t>VBL</t>
-  </si>
-  <si>
-    <t>ICICIGI</t>
-  </si>
-  <si>
-    <t>MARUTI</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>COALINDIA</t>
-  </si>
-  <si>
-    <t>TECHM</t>
-  </si>
-  <si>
-    <t>HDFCBANK</t>
-  </si>
-  <si>
-    <t>SIEMENS</t>
-  </si>
-  <si>
-    <t>INDUSINDBK</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>ASIANPAINT</t>
-  </si>
-  <si>
-    <t>WIPRO</t>
-  </si>
-  <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>ADANIPORTS</t>
-  </si>
-  <si>
-    <t>INDIGO</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>TRENT</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>IOC</t>
+    <t>AWL India Limited</t>
+  </si>
+  <si>
+    <t>BRITANNIA India Limited</t>
+  </si>
+  <si>
+    <t>ULTRACEMCO India Limited</t>
+  </si>
+  <si>
+    <t>GODREJCP India Limited</t>
+  </si>
+  <si>
+    <t>AMBUJACEM India Limited</t>
+  </si>
+  <si>
+    <t>CIPLA India Limited</t>
+  </si>
+  <si>
+    <t>INDIGO India Limited</t>
+  </si>
+  <si>
+    <t>BPCL India Limited</t>
+  </si>
+  <si>
+    <t>AXISBANK India Limited</t>
+  </si>
+  <si>
+    <t>ADANIENT India Limited</t>
+  </si>
+  <si>
+    <t>ICICIPRULI India Limited</t>
+  </si>
+  <si>
+    <t>PFC India Limited</t>
+  </si>
+  <si>
+    <t>JIOFIN India Limited</t>
+  </si>
+  <si>
+    <t>TECHM India Limited</t>
+  </si>
+  <si>
+    <t>POLYCAB India Limited</t>
+  </si>
+  <si>
+    <t>ADANIPORTS India Limited</t>
+  </si>
+  <si>
+    <t>BAJFINANCE India Limited</t>
+  </si>
+  <si>
+    <t>NESTLEIND India Limited</t>
+  </si>
+  <si>
+    <t>BOSCHLTD India Limited</t>
+  </si>
+  <si>
+    <t>POLICYBZR India Limited</t>
   </si>
   <si>
     <t>HINDUNILVR India Limited</t>
   </si>
   <si>
-    <t>ICICIPRULI India Limited</t>
+    <t>LODHA India Limited</t>
+  </si>
+  <si>
+    <t>MANKIND India Limited</t>
+  </si>
+  <si>
+    <t>DIVISLAB India Limited</t>
   </si>
   <si>
     <t>ABB India Limited</t>
   </si>
   <si>
+    <t>PERSISTENT India Limited</t>
+  </si>
+  <si>
+    <t>ZOMATO India Limited</t>
+  </si>
+  <si>
+    <t>TCS India Limited</t>
+  </si>
+  <si>
+    <t>PAYTM India Limited</t>
+  </si>
+  <si>
+    <t>COALINDIA India Limited</t>
+  </si>
+  <si>
+    <t>KOTAKBANK India Limited</t>
+  </si>
+  <si>
+    <t>HAL India Limited</t>
+  </si>
+  <si>
+    <t>ITC India Limited</t>
+  </si>
+  <si>
+    <t>TATAELXSI India Limited</t>
+  </si>
+  <si>
+    <t>TATACHEM India Limited</t>
+  </si>
+  <si>
+    <t>TATACOMM India Limited</t>
+  </si>
+  <si>
+    <t>TATASTEEL India Limited</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN India Limited</t>
+  </si>
+  <si>
+    <t>PAGEIND India Limited</t>
+  </si>
+  <si>
+    <t>BAJAJFINSV India Limited</t>
+  </si>
+  <si>
+    <t>WIPRO India Limited</t>
+  </si>
+  <si>
+    <t>COLPAL India Limited</t>
+  </si>
+  <si>
+    <t>ASIANPAINT India Limited</t>
+  </si>
+  <si>
+    <t>IRCTC India Limited</t>
+  </si>
+  <si>
+    <t>SIEMENS India Limited</t>
+  </si>
+  <si>
+    <t>ONGC India Limited</t>
+  </si>
+  <si>
+    <t>VEDL India Limited</t>
+  </si>
+  <si>
+    <t>MARUTI India Limited</t>
+  </si>
+  <si>
+    <t>BHARTIARTL India Limited</t>
+  </si>
+  <si>
+    <t>INTERGLOBE India Limited</t>
+  </si>
+  <si>
+    <t>LTIM India Limited</t>
+  </si>
+  <si>
+    <t>EICHERMOT India Limited</t>
+  </si>
+  <si>
+    <t>SBIN India Limited</t>
+  </si>
+  <si>
+    <t>TATAMOTORS India Limited</t>
+  </si>
+  <si>
+    <t>ICICIBANK India Limited</t>
+  </si>
+  <si>
+    <t>PIDILITIND India Limited</t>
+  </si>
+  <si>
+    <t>DLF India Limited</t>
+  </si>
+  <si>
+    <t>SUNPHARMA India Limited</t>
+  </si>
+  <si>
+    <t>TRENT India Limited</t>
+  </si>
+  <si>
+    <t>POWERGRID India Limited</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP India Limited</t>
+  </si>
+  <si>
+    <t>INFY India Limited</t>
+  </si>
+  <si>
+    <t>HEROMOTOCO India Limited</t>
+  </si>
+  <si>
+    <t>CHOLAFIN India Limited</t>
+  </si>
+  <si>
+    <t>RECLTD India Limited</t>
+  </si>
+  <si>
     <t>GAIL India Limited</t>
   </si>
   <si>
+    <t>M_M India Limited</t>
+  </si>
+  <si>
+    <t>MOTHERSON India Limited</t>
+  </si>
+  <si>
+    <t>HDFCBANK India Limited</t>
+  </si>
+  <si>
+    <t>JSWSTEEL India Limited</t>
+  </si>
+  <si>
+    <t>VBL India Limited</t>
+  </si>
+  <si>
+    <t>TITAN India Limited</t>
+  </si>
+  <si>
+    <t>SRF India Limited</t>
+  </si>
+  <si>
+    <t>LT India Limited</t>
+  </si>
+  <si>
+    <t>GRASIM India Limited</t>
+  </si>
+  <si>
+    <t>ICICIGI India Limited</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO India Limited</t>
+  </si>
+  <si>
+    <t>HCLTECH India Limited</t>
+  </si>
+  <si>
+    <t>DRREDDY India Limited</t>
+  </si>
+  <si>
+    <t>SAIL India Limited</t>
+  </si>
+  <si>
+    <t>BEL India Limited</t>
+  </si>
+  <si>
     <t>CANBK India Limited</t>
   </si>
   <si>
-    <t>RECLTD India Limited</t>
-  </si>
-  <si>
-    <t>SBIN India Limited</t>
-  </si>
-  <si>
-    <t>LT India Limited</t>
-  </si>
-  <si>
-    <t>AMBUJACEM India Limited</t>
-  </si>
-  <si>
-    <t>PAYTM India Limited</t>
-  </si>
-  <si>
-    <t>HCLTECH India Limited</t>
-  </si>
-  <si>
-    <t>ADANIENT India Limited</t>
+    <t>IOC India Limited</t>
+  </si>
+  <si>
+    <t>TATAINVEST India Limited</t>
   </si>
   <si>
     <t>HDFCLIFE India Limited</t>
   </si>
   <si>
-    <t>CHOLAFIN India Limited</t>
-  </si>
-  <si>
-    <t>PAGEIND India Limited</t>
-  </si>
-  <si>
-    <t>TATAELXSI India Limited</t>
-  </si>
-  <si>
-    <t>SRF India Limited</t>
-  </si>
-  <si>
-    <t>BRITANNIA India Limited</t>
-  </si>
-  <si>
-    <t>TATAMOTORS India Limited</t>
-  </si>
-  <si>
-    <t>CIPLA India Limited</t>
-  </si>
-  <si>
-    <t>MANKIND India Limited</t>
-  </si>
-  <si>
-    <t>IRCTC India Limited</t>
-  </si>
-  <si>
-    <t>JSWSTEEL India Limited</t>
-  </si>
-  <si>
-    <t>KOTAKBANK India Limited</t>
-  </si>
-  <si>
-    <t>GRASIM India Limited</t>
-  </si>
-  <si>
-    <t>HEROMOTOCO India Limited</t>
-  </si>
-  <si>
-    <t>TATAINVEST India Limited</t>
-  </si>
-  <si>
-    <t>DRREDDY India Limited</t>
-  </si>
-  <si>
-    <t>EICHERMOT India Limited</t>
-  </si>
-  <si>
-    <t>INTERGLOBE India Limited</t>
-  </si>
-  <si>
-    <t>NESTLEIND India Limited</t>
-  </si>
-  <si>
-    <t>POWERGRID India Limited</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP India Limited</t>
-  </si>
-  <si>
-    <t>BAJFINANCE India Limited</t>
-  </si>
-  <si>
     <t>MUTHOOTFIN India Limited</t>
   </si>
   <si>
     <t>IDFCFIRSTB India Limited</t>
   </si>
   <si>
-    <t>PIDILITIND India Limited</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO India Limited</t>
-  </si>
-  <si>
-    <t>TATACOMM India Limited</t>
-  </si>
-  <si>
-    <t>AXISBANK India Limited</t>
-  </si>
-  <si>
-    <t>POLYCAB India Limited</t>
-  </si>
-  <si>
-    <t>POLICYBZR India Limited</t>
-  </si>
-  <si>
-    <t>PFC India Limited</t>
-  </si>
-  <si>
-    <t>LTIM India Limited</t>
-  </si>
-  <si>
-    <t>DIVISLAB India Limited</t>
-  </si>
-  <si>
-    <t>MOTHERSON India Limited</t>
+    <t>NTPC India Limited</t>
+  </si>
+  <si>
+    <t>INDUSINDBK India Limited</t>
+  </si>
+  <si>
+    <t>VARUNBEV India Limited</t>
+  </si>
+  <si>
+    <t>MAXHEALTH India Limited</t>
   </si>
   <si>
     <t>RELIANCE India Limited</t>
   </si>
   <si>
-    <t>M_M India Limited</t>
-  </si>
-  <si>
-    <t>TITAN India Limited</t>
-  </si>
-  <si>
-    <t>TATASTEEL India Limited</t>
-  </si>
-  <si>
-    <t>ZOMATO India Limited</t>
-  </si>
-  <si>
-    <t>DLF India Limited</t>
-  </si>
-  <si>
-    <t>VARUNBEV India Limited</t>
-  </si>
-  <si>
-    <t>PERSISTENT India Limited</t>
-  </si>
-  <si>
-    <t>ICICIBANK India Limited</t>
-  </si>
-  <si>
-    <t>SUNPHARMA India Limited</t>
-  </si>
-  <si>
-    <t>GODREJCP India Limited</t>
-  </si>
-  <si>
-    <t>SAIL India Limited</t>
-  </si>
-  <si>
-    <t>VEDL India Limited</t>
-  </si>
-  <si>
-    <t>ONGC India Limited</t>
-  </si>
-  <si>
-    <t>TATACHEM India Limited</t>
-  </si>
-  <si>
-    <t>ULTRACEMCO India Limited</t>
-  </si>
-  <si>
-    <t>COLPAL India Limited</t>
-  </si>
-  <si>
-    <t>BHARTIARTL India Limited</t>
-  </si>
-  <si>
-    <t>TCS India Limited</t>
-  </si>
-  <si>
-    <t>AWL India Limited</t>
-  </si>
-  <si>
-    <t>BOSCHLTD India Limited</t>
-  </si>
-  <si>
-    <t>HAL India Limited</t>
-  </si>
-  <si>
-    <t>JIOFIN India Limited</t>
-  </si>
-  <si>
-    <t>LODHA India Limited</t>
-  </si>
-  <si>
-    <t>VBL India Limited</t>
-  </si>
-  <si>
-    <t>ICICIGI India Limited</t>
-  </si>
-  <si>
-    <t>MARUTI India Limited</t>
-  </si>
-  <si>
-    <t>INFY India Limited</t>
-  </si>
-  <si>
-    <t>COALINDIA India Limited</t>
-  </si>
-  <si>
-    <t>TECHM India Limited</t>
-  </si>
-  <si>
-    <t>HDFCBANK India Limited</t>
-  </si>
-  <si>
-    <t>SIEMENS India Limited</t>
-  </si>
-  <si>
-    <t>INDUSINDBK India Limited</t>
-  </si>
-  <si>
-    <t>MAXHEALTH India Limited</t>
-  </si>
-  <si>
-    <t>ASIANPAINT India Limited</t>
-  </si>
-  <si>
-    <t>WIPRO India Limited</t>
-  </si>
-  <si>
-    <t>BPCL India Limited</t>
-  </si>
-  <si>
-    <t>ADANIPORTS India Limited</t>
-  </si>
-  <si>
-    <t>INDIGO India Limited</t>
-  </si>
-  <si>
-    <t>BAJAJFINSV India Limited</t>
-  </si>
-  <si>
-    <t>ITC India Limited</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN India Limited</t>
-  </si>
-  <si>
-    <t>BEL India Limited</t>
-  </si>
-  <si>
-    <t>TRENT India Limited</t>
-  </si>
-  <si>
-    <t>NTPC India Limited</t>
-  </si>
-  <si>
-    <t>IOC India Limited</t>
+    <t>Metals</t>
+  </si>
+  <si>
+    <t>Pharma</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Automobile</t>
+  </si>
+  <si>
+    <t>Power</t>
   </si>
   <si>
     <t>IT</t>
@@ -610,25 +625,10 @@
     <t>Oil &amp; Gas</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>Consumer Goods</t>
   </si>
   <si>
-    <t>Automobile</t>
-  </si>
-  <si>
     <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Metals</t>
-  </si>
-  <si>
-    <t>Pharma</t>
-  </si>
-  <si>
-    <t>Power</t>
   </si>
   <si>
     <t>Caution</t>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -1050,25 +1050,25 @@
         <v>196</v>
       </c>
       <c r="E2">
-        <v>34.67</v>
+        <v>34.35</v>
       </c>
       <c r="F2">
-        <v>2.95</v>
+        <v>5.2</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>25.76</v>
       </c>
       <c r="H2">
-        <v>0.92</v>
+        <v>0.27</v>
       </c>
       <c r="I2">
-        <v>25.43</v>
+        <v>24.83</v>
       </c>
       <c r="J2">
-        <v>20.7</v>
+        <v>20.355</v>
       </c>
       <c r="K2">
-        <v>67.48999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="L2" t="s">
         <v>205</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1088,25 +1088,25 @@
         <v>196</v>
       </c>
       <c r="E3">
-        <v>34.15</v>
+        <v>31.27</v>
       </c>
       <c r="F3">
-        <v>2.2</v>
+        <v>5.89</v>
       </c>
       <c r="G3">
-        <v>25.61</v>
+        <v>23.45</v>
       </c>
       <c r="H3">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="I3">
-        <v>26.63</v>
+        <v>28.1</v>
       </c>
       <c r="J3">
-        <v>20.7</v>
+        <v>20.355</v>
       </c>
       <c r="K3">
-        <v>64.98</v>
+        <v>53.62</v>
       </c>
       <c r="L3" t="s">
         <v>205</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1123,36 +1123,36 @@
         <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E4">
-        <v>34.08</v>
+        <v>32.66</v>
       </c>
       <c r="F4">
-        <v>5.87</v>
+        <v>2.79</v>
       </c>
       <c r="G4">
-        <v>25.56</v>
+        <v>24.49</v>
       </c>
       <c r="H4">
-        <v>1.79</v>
+        <v>0.59</v>
       </c>
       <c r="I4">
-        <v>29.28</v>
+        <v>27.12</v>
       </c>
       <c r="J4">
-        <v>20.7</v>
+        <v>21.815</v>
       </c>
       <c r="K4">
-        <v>64.64</v>
+        <v>49.71</v>
       </c>
       <c r="L4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -1164,33 +1164,33 @@
         <v>197</v>
       </c>
       <c r="E5">
-        <v>34.2</v>
+        <v>31.29</v>
       </c>
       <c r="F5">
-        <v>2.29</v>
+        <v>5.98</v>
       </c>
       <c r="G5">
-        <v>25.65</v>
+        <v>23.47</v>
       </c>
       <c r="H5">
-        <v>0.95</v>
+        <v>0.4</v>
       </c>
       <c r="I5">
-        <v>28.46</v>
+        <v>22.96</v>
       </c>
       <c r="J5">
-        <v>21.26</v>
+        <v>21.815</v>
       </c>
       <c r="K5">
-        <v>60.87</v>
+        <v>43.43</v>
       </c>
       <c r="L5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -1199,36 +1199,36 @@
         <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E6">
-        <v>31.51</v>
+        <v>34.89</v>
       </c>
       <c r="F6">
-        <v>3.9</v>
+        <v>5.94</v>
       </c>
       <c r="G6">
-        <v>23.63</v>
+        <v>26.17</v>
       </c>
       <c r="H6">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="I6">
-        <v>22.58</v>
+        <v>26.97</v>
       </c>
       <c r="J6">
-        <v>20.7</v>
+        <v>24.415</v>
       </c>
       <c r="K6">
-        <v>52.22</v>
+        <v>42.9</v>
       </c>
       <c r="L6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -1237,28 +1237,28 @@
         <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E7">
-        <v>34.52</v>
+        <v>29.88</v>
       </c>
       <c r="F7">
-        <v>2.03</v>
+        <v>3.62</v>
       </c>
       <c r="G7">
-        <v>25.89</v>
+        <v>22.41</v>
       </c>
       <c r="H7">
-        <v>0.75</v>
+        <v>2.2</v>
       </c>
       <c r="I7">
-        <v>30.74</v>
+        <v>23.47</v>
       </c>
       <c r="J7">
-        <v>23.45</v>
+        <v>21.815</v>
       </c>
       <c r="K7">
-        <v>47.21</v>
+        <v>36.97</v>
       </c>
       <c r="L7" t="s">
         <v>206</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
@@ -1275,28 +1275,28 @@
         <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E8">
-        <v>33.49</v>
+        <v>33.18</v>
       </c>
       <c r="F8">
-        <v>3.34</v>
+        <v>4.68</v>
       </c>
       <c r="G8">
-        <v>25.12</v>
+        <v>24.88</v>
       </c>
       <c r="H8">
-        <v>0.6</v>
+        <v>0.23</v>
       </c>
       <c r="I8">
-        <v>28.62</v>
+        <v>27.84</v>
       </c>
       <c r="J8">
-        <v>23.45</v>
+        <v>24.67</v>
       </c>
       <c r="K8">
-        <v>42.81</v>
+        <v>34.5</v>
       </c>
       <c r="L8" t="s">
         <v>206</v>
@@ -1304,7 +1304,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -1313,28 +1313,28 @@
         <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E9">
-        <v>30.25</v>
+        <v>30.69</v>
       </c>
       <c r="F9">
-        <v>4.02</v>
+        <v>5.01</v>
       </c>
       <c r="G9">
-        <v>22.69</v>
+        <v>23.02</v>
       </c>
       <c r="H9">
-        <v>0.19</v>
+        <v>1.28</v>
       </c>
       <c r="I9">
-        <v>24.29</v>
+        <v>21.8</v>
       </c>
       <c r="J9">
-        <v>21.26</v>
+        <v>24.67</v>
       </c>
       <c r="K9">
-        <v>42.29</v>
+        <v>24.4</v>
       </c>
       <c r="L9" t="s">
         <v>206</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
@@ -1351,28 +1351,28 @@
         <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E10">
-        <v>32.39</v>
+        <v>34.74</v>
       </c>
       <c r="F10">
-        <v>2.9</v>
+        <v>5.85</v>
       </c>
       <c r="G10">
-        <v>24.29</v>
+        <v>26.06</v>
       </c>
       <c r="H10">
-        <v>0.66</v>
+        <v>1.37</v>
       </c>
       <c r="I10">
-        <v>30.33</v>
+        <v>24.3</v>
       </c>
       <c r="J10">
-        <v>23.45</v>
+        <v>27.935</v>
       </c>
       <c r="K10">
-        <v>38.12</v>
+        <v>24.36</v>
       </c>
       <c r="L10" t="s">
         <v>206</v>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -1389,28 +1389,28 @@
         <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E11">
-        <v>31.6</v>
+        <v>30.19</v>
       </c>
       <c r="F11">
-        <v>3.13</v>
+        <v>5.36</v>
       </c>
       <c r="G11">
-        <v>23.7</v>
+        <v>22.64</v>
       </c>
       <c r="H11">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="I11">
-        <v>24.16</v>
+        <v>25.11</v>
       </c>
       <c r="J11">
-        <v>23.025</v>
+        <v>24.415</v>
       </c>
       <c r="K11">
-        <v>37.24</v>
+        <v>23.65</v>
       </c>
       <c r="L11" t="s">
         <v>206</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
@@ -1427,28 +1427,28 @@
         <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E12">
-        <v>34.87</v>
+        <v>33.92</v>
       </c>
       <c r="F12">
-        <v>4.23</v>
+        <v>3.72</v>
       </c>
       <c r="G12">
-        <v>26.15</v>
+        <v>25.44</v>
       </c>
       <c r="H12">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="I12">
-        <v>25.36</v>
+        <v>25.79</v>
       </c>
       <c r="J12">
-        <v>25.76</v>
+        <v>27.88</v>
       </c>
       <c r="K12">
-        <v>35.36</v>
+        <v>21.66</v>
       </c>
       <c r="L12" t="s">
         <v>206</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
@@ -1465,28 +1465,28 @@
         <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E13">
-        <v>31.41</v>
+        <v>33.59</v>
       </c>
       <c r="F13">
-        <v>3.52</v>
+        <v>3.63</v>
       </c>
       <c r="G13">
-        <v>23.56</v>
+        <v>25.19</v>
       </c>
       <c r="H13">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="I13">
-        <v>25.15</v>
+        <v>26.14</v>
       </c>
       <c r="J13">
-        <v>23.45</v>
+        <v>27.935</v>
       </c>
       <c r="K13">
-        <v>33.94</v>
+        <v>20.24</v>
       </c>
       <c r="L13" t="s">
         <v>206</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -1503,28 +1503,28 @@
         <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E14">
-        <v>33.72</v>
+        <v>29.18</v>
       </c>
       <c r="F14">
-        <v>3.09</v>
+        <v>2.76</v>
       </c>
       <c r="G14">
-        <v>25.29</v>
+        <v>21.88</v>
       </c>
       <c r="H14">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="I14">
-        <v>21.46</v>
+        <v>26.3</v>
       </c>
       <c r="J14">
-        <v>25.76</v>
+        <v>24.415</v>
       </c>
       <c r="K14">
-        <v>30.9</v>
+        <v>19.52</v>
       </c>
       <c r="L14" t="s">
         <v>206</v>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
@@ -1541,28 +1541,28 @@
         <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E15">
-        <v>26.97</v>
+        <v>34.66</v>
       </c>
       <c r="F15">
-        <v>5.24</v>
+        <v>2.48</v>
       </c>
       <c r="G15">
-        <v>20.23</v>
+        <v>25.99</v>
       </c>
       <c r="H15">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="I15">
-        <v>24.09</v>
+        <v>31.44</v>
       </c>
       <c r="J15">
-        <v>20.7</v>
+        <v>30.1</v>
       </c>
       <c r="K15">
-        <v>30.29</v>
+        <v>15.15</v>
       </c>
       <c r="L15" t="s">
         <v>206</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -1579,28 +1579,28 @@
         <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E16">
-        <v>33.31</v>
+        <v>24.87</v>
       </c>
       <c r="F16">
-        <v>2.29</v>
+        <v>4.43</v>
       </c>
       <c r="G16">
-        <v>24.98</v>
+        <v>18.65</v>
       </c>
       <c r="H16">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="I16">
-        <v>30.82</v>
+        <v>25.48</v>
       </c>
       <c r="J16">
-        <v>25.76</v>
+        <v>21.815</v>
       </c>
       <c r="K16">
-        <v>29.31</v>
+        <v>14</v>
       </c>
       <c r="L16" t="s">
         <v>206</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
@@ -1617,28 +1617,28 @@
         <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E17">
-        <v>34.35</v>
+        <v>27.8</v>
       </c>
       <c r="F17">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="G17">
-        <v>25.76</v>
+        <v>20.85</v>
       </c>
       <c r="H17">
-        <v>1.45</v>
+        <v>0.2</v>
       </c>
       <c r="I17">
-        <v>23.99</v>
+        <v>26.84</v>
       </c>
       <c r="J17">
-        <v>27.04</v>
+        <v>24.67</v>
       </c>
       <c r="K17">
-        <v>27.03</v>
+        <v>12.69</v>
       </c>
       <c r="L17" t="s">
         <v>206</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>28</v>
@@ -1655,28 +1655,28 @@
         <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E18">
-        <v>33.09</v>
+        <v>33.53</v>
       </c>
       <c r="F18">
-        <v>2.43</v>
+        <v>3.64</v>
       </c>
       <c r="G18">
-        <v>24.82</v>
+        <v>25.15</v>
       </c>
       <c r="H18">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="I18">
-        <v>27</v>
+        <v>28.16</v>
       </c>
       <c r="J18">
-        <v>26.345</v>
+        <v>29.825</v>
       </c>
       <c r="K18">
-        <v>25.6</v>
+        <v>12.42</v>
       </c>
       <c r="L18" t="s">
         <v>206</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
@@ -1693,28 +1693,28 @@
         <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E19">
-        <v>32.99</v>
+        <v>22.81</v>
       </c>
       <c r="F19">
-        <v>4.2</v>
+        <v>2.16</v>
       </c>
       <c r="G19">
-        <v>24.74</v>
+        <v>17.11</v>
       </c>
       <c r="H19">
-        <v>0.51</v>
+        <v>1.27</v>
       </c>
       <c r="I19">
-        <v>23.54</v>
+        <v>23.26</v>
       </c>
       <c r="J19">
-        <v>26.345</v>
+        <v>20.355</v>
       </c>
       <c r="K19">
-        <v>25.22</v>
+        <v>12.06</v>
       </c>
       <c r="L19" t="s">
         <v>206</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
         <v>30</v>
@@ -1731,28 +1731,28 @@
         <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E20">
-        <v>28.28</v>
+        <v>32.99</v>
       </c>
       <c r="F20">
-        <v>2.55</v>
+        <v>3.44</v>
       </c>
       <c r="G20">
-        <v>21.21</v>
+        <v>24.74</v>
       </c>
       <c r="H20">
-        <v>1.97</v>
+        <v>0.71</v>
       </c>
       <c r="I20">
-        <v>24.35</v>
+        <v>31.12</v>
       </c>
       <c r="J20">
-        <v>23.025</v>
+        <v>29.825</v>
       </c>
       <c r="K20">
-        <v>22.82</v>
+        <v>10.61</v>
       </c>
       <c r="L20" t="s">
         <v>206</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -1769,28 +1769,28 @@
         <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E21">
-        <v>25.16</v>
+        <v>27.17</v>
       </c>
       <c r="F21">
-        <v>3.5</v>
+        <v>5.57</v>
       </c>
       <c r="G21">
-        <v>18.87</v>
+        <v>20.38</v>
       </c>
       <c r="H21">
-        <v>2.2</v>
+        <v>0.44</v>
       </c>
       <c r="I21">
-        <v>29.98</v>
+        <v>27.34</v>
       </c>
       <c r="J21">
-        <v>20.545</v>
+        <v>24.67</v>
       </c>
       <c r="K21">
-        <v>22.46</v>
+        <v>10.13</v>
       </c>
       <c r="L21" t="s">
         <v>206</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
@@ -1807,28 +1807,28 @@
         <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E22">
-        <v>25.83</v>
+        <v>30.67</v>
       </c>
       <c r="F22">
-        <v>3.83</v>
+        <v>2.26</v>
       </c>
       <c r="G22">
-        <v>19.37</v>
+        <v>23</v>
       </c>
       <c r="H22">
-        <v>0.42</v>
+        <v>0.92</v>
       </c>
       <c r="I22">
-        <v>24.66</v>
+        <v>26.68</v>
       </c>
       <c r="J22">
-        <v>21.26</v>
+        <v>27.88</v>
       </c>
       <c r="K22">
-        <v>21.5</v>
+        <v>10.01</v>
       </c>
       <c r="L22" t="s">
         <v>206</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
@@ -1845,28 +1845,28 @@
         <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E23">
-        <v>24.95</v>
+        <v>30.65</v>
       </c>
       <c r="F23">
-        <v>4.97</v>
+        <v>2.24</v>
       </c>
       <c r="G23">
-        <v>18.71</v>
+        <v>22.99</v>
       </c>
       <c r="H23">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="I23">
-        <v>22.12</v>
+        <v>24.84</v>
       </c>
       <c r="J23">
-        <v>20.545</v>
+        <v>27.935</v>
       </c>
       <c r="K23">
-        <v>21.44</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L23" t="s">
         <v>206</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -1883,28 +1883,28 @@
         <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E24">
-        <v>24.96</v>
+        <v>32.89</v>
       </c>
       <c r="F24">
-        <v>5.41</v>
+        <v>5.79</v>
       </c>
       <c r="G24">
-        <v>18.72</v>
+        <v>24.67</v>
       </c>
       <c r="H24">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
       <c r="I24">
-        <v>25.54</v>
+        <v>24.66</v>
       </c>
       <c r="J24">
-        <v>21.26</v>
+        <v>30.1</v>
       </c>
       <c r="K24">
-        <v>17.4</v>
+        <v>9.27</v>
       </c>
       <c r="L24" t="s">
         <v>206</v>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
         <v>35</v>
@@ -1921,28 +1921,28 @@
         <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E25">
-        <v>31.74</v>
+        <v>32.53</v>
       </c>
       <c r="F25">
-        <v>3.01</v>
+        <v>2.48</v>
       </c>
       <c r="G25">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="H25">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="I25">
-        <v>26.85</v>
+        <v>29.72</v>
       </c>
       <c r="J25">
-        <v>27.04</v>
+        <v>29.825</v>
       </c>
       <c r="K25">
-        <v>17.38</v>
+        <v>9.07</v>
       </c>
       <c r="L25" t="s">
         <v>206</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
@@ -1959,28 +1959,28 @@
         <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E26">
-        <v>24.11</v>
+        <v>30.28</v>
       </c>
       <c r="F26">
-        <v>2.88</v>
+        <v>4.85</v>
       </c>
       <c r="G26">
-        <v>18.08</v>
+        <v>22.71</v>
       </c>
       <c r="H26">
-        <v>0.54</v>
+        <v>1.79</v>
       </c>
       <c r="I26">
-        <v>22.25</v>
+        <v>22.33</v>
       </c>
       <c r="J26">
-        <v>20.545</v>
+        <v>27.88</v>
       </c>
       <c r="K26">
-        <v>17.35</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L26" t="s">
         <v>206</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
@@ -1997,28 +1997,28 @@
         <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E27">
-        <v>26.84</v>
+        <v>34.76</v>
       </c>
       <c r="F27">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="G27">
-        <v>20.13</v>
+        <v>26.07</v>
       </c>
       <c r="H27">
-        <v>4.07</v>
+        <v>0.36</v>
       </c>
       <c r="I27">
-        <v>27.08</v>
+        <v>28.46</v>
       </c>
       <c r="J27">
-        <v>23.025</v>
+        <v>32.135</v>
       </c>
       <c r="K27">
-        <v>16.57</v>
+        <v>8.17</v>
       </c>
       <c r="L27" t="s">
         <v>206</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
         <v>38</v>
@@ -2035,28 +2035,28 @@
         <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E28">
-        <v>27.12</v>
+        <v>34.75</v>
       </c>
       <c r="F28">
-        <v>5.01</v>
+        <v>3.78</v>
       </c>
       <c r="G28">
-        <v>20.34</v>
+        <v>26.06</v>
       </c>
       <c r="H28">
-        <v>0.26</v>
+        <v>0.98</v>
       </c>
       <c r="I28">
-        <v>21.82</v>
+        <v>24.07</v>
       </c>
       <c r="J28">
-        <v>23.45</v>
+        <v>32.135</v>
       </c>
       <c r="K28">
-        <v>15.65</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L28" t="s">
         <v>206</v>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
         <v>39</v>
@@ -2073,28 +2073,28 @@
         <v>131</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E29">
-        <v>23.39</v>
+        <v>32.5</v>
       </c>
       <c r="F29">
-        <v>4.92</v>
+        <v>3.68</v>
       </c>
       <c r="G29">
-        <v>17.54</v>
+        <v>24.38</v>
       </c>
       <c r="H29">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="I29">
-        <v>22.36</v>
+        <v>29.22</v>
       </c>
       <c r="J29">
-        <v>20.545</v>
+        <v>30.1</v>
       </c>
       <c r="K29">
-        <v>13.85</v>
+        <v>7.97</v>
       </c>
       <c r="L29" t="s">
         <v>206</v>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
@@ -2111,28 +2111,28 @@
         <v>132</v>
       </c>
       <c r="D30" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E30">
-        <v>29.15</v>
+        <v>32.06</v>
       </c>
       <c r="F30">
-        <v>5.97</v>
+        <v>2.78</v>
       </c>
       <c r="G30">
-        <v>21.86</v>
+        <v>24.04</v>
       </c>
       <c r="H30">
-        <v>1.66</v>
+        <v>0.31</v>
       </c>
       <c r="I30">
-        <v>24.22</v>
+        <v>25.78</v>
       </c>
       <c r="J30">
-        <v>25.76</v>
+        <v>29.825</v>
       </c>
       <c r="K30">
-        <v>13.16</v>
+        <v>7.49</v>
       </c>
       <c r="L30" t="s">
         <v>206</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
@@ -2149,28 +2149,28 @@
         <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E31">
-        <v>33.25</v>
+        <v>26.24</v>
       </c>
       <c r="F31">
-        <v>5.02</v>
+        <v>2.33</v>
       </c>
       <c r="G31">
-        <v>24.94</v>
+        <v>19.68</v>
       </c>
       <c r="H31">
-        <v>0.6899999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="I31">
-        <v>28.62</v>
+        <v>24.71</v>
       </c>
       <c r="J31">
-        <v>29.64</v>
+        <v>24.415</v>
       </c>
       <c r="K31">
-        <v>12.18</v>
+        <v>7.47</v>
       </c>
       <c r="L31" t="s">
         <v>206</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
         <v>42</v>
@@ -2187,28 +2187,28 @@
         <v>134</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E32">
-        <v>29.5</v>
+        <v>34.52</v>
       </c>
       <c r="F32">
-        <v>2.22</v>
+        <v>4.69</v>
       </c>
       <c r="G32">
-        <v>22.12</v>
+        <v>25.89</v>
       </c>
       <c r="H32">
-        <v>1.27</v>
+        <v>0.24</v>
       </c>
       <c r="I32">
-        <v>25.26</v>
+        <v>25.73</v>
       </c>
       <c r="J32">
-        <v>26.345</v>
+        <v>32.135</v>
       </c>
       <c r="K32">
-        <v>11.98</v>
+        <v>7.42</v>
       </c>
       <c r="L32" t="s">
         <v>206</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -2225,28 +2225,28 @@
         <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E33">
-        <v>29.49</v>
+        <v>29.79</v>
       </c>
       <c r="F33">
-        <v>5.68</v>
+        <v>5.22</v>
       </c>
       <c r="G33">
-        <v>22.12</v>
+        <v>22.34</v>
       </c>
       <c r="H33">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="I33">
-        <v>29.49</v>
+        <v>24.15</v>
       </c>
       <c r="J33">
-        <v>26.345</v>
+        <v>27.88</v>
       </c>
       <c r="K33">
-        <v>11.94</v>
+        <v>6.85</v>
       </c>
       <c r="L33" t="s">
         <v>206</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
         <v>44</v>
@@ -2263,28 +2263,28 @@
         <v>136</v>
       </c>
       <c r="D34" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E34">
-        <v>29.3</v>
+        <v>29.51</v>
       </c>
       <c r="F34">
-        <v>5.4</v>
+        <v>4.74</v>
       </c>
       <c r="G34">
-        <v>21.98</v>
+        <v>22.13</v>
       </c>
       <c r="H34">
-        <v>0.47</v>
+        <v>2.15</v>
       </c>
       <c r="I34">
-        <v>21.22</v>
+        <v>26.88</v>
       </c>
       <c r="J34">
-        <v>26.345</v>
+        <v>27.935</v>
       </c>
       <c r="K34">
-        <v>11.22</v>
+        <v>5.64</v>
       </c>
       <c r="L34" t="s">
         <v>206</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="B35" t="s">
         <v>45</v>
@@ -2301,28 +2301,28 @@
         <v>137</v>
       </c>
       <c r="D35" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E35">
-        <v>25.4</v>
+        <v>33.35</v>
       </c>
       <c r="F35">
-        <v>3.95</v>
+        <v>5.35</v>
       </c>
       <c r="G35">
-        <v>19.05</v>
+        <v>25.01</v>
       </c>
       <c r="H35">
-        <v>0.4</v>
+        <v>1.45</v>
       </c>
       <c r="I35">
-        <v>28.4</v>
+        <v>23.54</v>
       </c>
       <c r="J35">
-        <v>23.025</v>
+        <v>32.135</v>
       </c>
       <c r="K35">
-        <v>10.31</v>
+        <v>3.78</v>
       </c>
       <c r="L35" t="s">
         <v>206</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
@@ -2342,25 +2342,25 @@
         <v>201</v>
       </c>
       <c r="E36">
-        <v>29.07</v>
+        <v>28.92</v>
       </c>
       <c r="F36">
-        <v>5.86</v>
+        <v>3.83</v>
       </c>
       <c r="G36">
-        <v>21.8</v>
+        <v>21.69</v>
       </c>
       <c r="H36">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="I36">
-        <v>21.89</v>
+        <v>23.32</v>
       </c>
       <c r="J36">
-        <v>27.04</v>
+        <v>27.88</v>
       </c>
       <c r="K36">
-        <v>7.51</v>
+        <v>3.73</v>
       </c>
       <c r="L36" t="s">
         <v>206</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
@@ -2377,28 +2377,28 @@
         <v>139</v>
       </c>
       <c r="D37" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E37">
-        <v>31.34</v>
+        <v>31.03</v>
       </c>
       <c r="F37">
-        <v>5.23</v>
+        <v>4.57</v>
       </c>
       <c r="G37">
-        <v>23.5</v>
+        <v>23.27</v>
       </c>
       <c r="H37">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="I37">
-        <v>23.93</v>
+        <v>24.49</v>
       </c>
       <c r="J37">
-        <v>29.64</v>
+        <v>30.1</v>
       </c>
       <c r="K37">
-        <v>5.74</v>
+        <v>3.09</v>
       </c>
       <c r="L37" t="s">
         <v>206</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
         <v>48</v>
@@ -2415,28 +2415,28 @@
         <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E38">
-        <v>30.98</v>
+        <v>30.66</v>
       </c>
       <c r="F38">
-        <v>5.91</v>
+        <v>5.86</v>
       </c>
       <c r="G38">
-        <v>23.24</v>
+        <v>23</v>
       </c>
       <c r="H38">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="I38">
-        <v>28.98</v>
+        <v>25.18</v>
       </c>
       <c r="J38">
-        <v>29.64</v>
+        <v>29.825</v>
       </c>
       <c r="K38">
-        <v>4.52</v>
+        <v>2.8</v>
       </c>
       <c r="L38" t="s">
         <v>206</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
         <v>49</v>
@@ -2453,28 +2453,28 @@
         <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E39">
-        <v>28.07</v>
+        <v>25.09</v>
       </c>
       <c r="F39">
-        <v>3.85</v>
+        <v>2.28</v>
       </c>
       <c r="G39">
-        <v>21.05</v>
+        <v>18.82</v>
       </c>
       <c r="H39">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="I39">
-        <v>21.53</v>
+        <v>25.3</v>
       </c>
       <c r="J39">
-        <v>27.04</v>
+        <v>24.415</v>
       </c>
       <c r="K39">
-        <v>3.81</v>
+        <v>2.76</v>
       </c>
       <c r="L39" t="s">
         <v>206</v>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s">
         <v>50</v>
@@ -2491,28 +2491,28 @@
         <v>142</v>
       </c>
       <c r="D40" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E40">
-        <v>22.04</v>
+        <v>25.32</v>
       </c>
       <c r="F40">
-        <v>5.77</v>
+        <v>2.55</v>
       </c>
       <c r="G40">
-        <v>16.53</v>
+        <v>18.99</v>
       </c>
       <c r="H40">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="I40">
-        <v>28.07</v>
+        <v>27.96</v>
       </c>
       <c r="J40">
-        <v>21.26</v>
+        <v>24.67</v>
       </c>
       <c r="K40">
-        <v>3.67</v>
+        <v>2.63</v>
       </c>
       <c r="L40" t="s">
         <v>206</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
@@ -2532,25 +2532,25 @@
         <v>204</v>
       </c>
       <c r="E41">
-        <v>30.68</v>
+        <v>32.82</v>
       </c>
       <c r="F41">
-        <v>5.15</v>
+        <v>4.56</v>
       </c>
       <c r="G41">
-        <v>23.01</v>
+        <v>24.62</v>
       </c>
       <c r="H41">
-        <v>1.37</v>
+        <v>0.34</v>
       </c>
       <c r="I41">
-        <v>27.19</v>
+        <v>26.24</v>
       </c>
       <c r="J41">
-        <v>29.64</v>
+        <v>32.135</v>
       </c>
       <c r="K41">
-        <v>3.51</v>
+        <v>2.13</v>
       </c>
       <c r="L41" t="s">
         <v>206</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
         <v>52</v>
@@ -2567,28 +2567,28 @@
         <v>144</v>
       </c>
       <c r="D42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E42">
-        <v>21.06</v>
+        <v>30.72</v>
       </c>
       <c r="F42">
-        <v>3.99</v>
+        <v>5.44</v>
       </c>
       <c r="G42">
-        <v>15.79</v>
+        <v>23.04</v>
       </c>
       <c r="H42">
-        <v>0.59</v>
+        <v>0.91</v>
       </c>
       <c r="I42">
-        <v>26.2</v>
+        <v>24.63</v>
       </c>
       <c r="J42">
-        <v>20.545</v>
+        <v>30.1</v>
       </c>
       <c r="K42">
-        <v>2.51</v>
+        <v>2.06</v>
       </c>
       <c r="L42" t="s">
         <v>206</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
@@ -2605,28 +2605,28 @@
         <v>145</v>
       </c>
       <c r="D43" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E43">
-        <v>26.37</v>
+        <v>20.73</v>
       </c>
       <c r="F43">
-        <v>2.16</v>
+        <v>5.46</v>
       </c>
       <c r="G43">
-        <v>19.78</v>
+        <v>15.55</v>
       </c>
       <c r="H43">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="I43">
-        <v>23.36</v>
+        <v>28.28</v>
       </c>
       <c r="J43">
-        <v>25.76</v>
+        <v>20.355</v>
       </c>
       <c r="K43">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="L43" t="s">
         <v>206</v>
@@ -2634,7 +2634,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
         <v>54</v>
@@ -2643,28 +2643,28 @@
         <v>146</v>
       </c>
       <c r="D44" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E44">
-        <v>30.17</v>
+        <v>28.4</v>
       </c>
       <c r="F44">
-        <v>2.73</v>
+        <v>5.24</v>
       </c>
       <c r="G44">
-        <v>22.63</v>
+        <v>21.3</v>
       </c>
       <c r="H44">
-        <v>0.32</v>
+        <v>0.75</v>
       </c>
       <c r="I44">
-        <v>25.76</v>
+        <v>26.29</v>
       </c>
       <c r="J44">
-        <v>29.64</v>
+        <v>27.935</v>
       </c>
       <c r="K44">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="L44" t="s">
         <v>206</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
         <v>55</v>
@@ -2681,28 +2681,28 @@
         <v>147</v>
       </c>
       <c r="D45" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E45">
-        <v>27.43</v>
+        <v>22.14</v>
       </c>
       <c r="F45">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="G45">
-        <v>20.57</v>
+        <v>16.6</v>
       </c>
       <c r="H45">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="I45">
-        <v>29.9</v>
+        <v>21.43</v>
       </c>
       <c r="J45">
-        <v>27.04</v>
+        <v>21.815</v>
       </c>
       <c r="K45">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="L45" t="s">
         <v>206</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
         <v>56</v>
@@ -2719,28 +2719,28 @@
         <v>148</v>
       </c>
       <c r="D46" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E46">
-        <v>23.2</v>
+        <v>20.58</v>
       </c>
       <c r="F46">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="G46">
-        <v>17.4</v>
+        <v>15.43</v>
       </c>
       <c r="H46">
-        <v>0.43</v>
+        <v>0.67</v>
       </c>
       <c r="I46">
-        <v>28.52</v>
+        <v>20.16</v>
       </c>
       <c r="J46">
-        <v>23.025</v>
+        <v>20.355</v>
       </c>
       <c r="K46">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="L46" t="s">
         <v>206</v>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>57</v>
@@ -2757,25 +2757,25 @@
         <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E47">
-        <v>21.26</v>
+        <v>30.1</v>
       </c>
       <c r="F47">
-        <v>5.92</v>
+        <v>4.68</v>
       </c>
       <c r="G47">
-        <v>15.94</v>
+        <v>22.58</v>
       </c>
       <c r="H47">
-        <v>2.51</v>
+        <v>1.37</v>
       </c>
       <c r="I47">
-        <v>21.14</v>
+        <v>27.11</v>
       </c>
       <c r="J47">
-        <v>21.26</v>
+        <v>30.1</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="B48" t="s">
         <v>58</v>
@@ -2795,25 +2795,25 @@
         <v>150</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E48">
-        <v>20.7</v>
+        <v>27.88</v>
       </c>
       <c r="F48">
-        <v>3.82</v>
+        <v>3.15</v>
       </c>
       <c r="G48">
-        <v>15.52</v>
+        <v>20.91</v>
       </c>
       <c r="H48">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="I48">
-        <v>23.65</v>
+        <v>22.58</v>
       </c>
       <c r="J48">
-        <v>20.7</v>
+        <v>27.88</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
         <v>59</v>
@@ -2836,25 +2836,25 @@
         <v>196</v>
       </c>
       <c r="E49">
-        <v>20.65</v>
+        <v>20.13</v>
       </c>
       <c r="F49">
-        <v>2.07</v>
+        <v>4.9</v>
       </c>
       <c r="G49">
-        <v>15.49</v>
+        <v>15.1</v>
       </c>
       <c r="H49">
-        <v>0.42</v>
+        <v>0.98</v>
       </c>
       <c r="I49">
-        <v>26.02</v>
+        <v>25.64</v>
       </c>
       <c r="J49">
-        <v>20.7</v>
+        <v>20.355</v>
       </c>
       <c r="K49">
-        <v>-0.24</v>
+        <v>-1.11</v>
       </c>
       <c r="L49" t="s">
         <v>206</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B50" t="s">
         <v>60</v>
@@ -2871,28 +2871,28 @@
         <v>152</v>
       </c>
       <c r="D50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E50">
-        <v>20.58</v>
+        <v>21.49</v>
       </c>
       <c r="F50">
-        <v>4.19</v>
+        <v>4.73</v>
       </c>
       <c r="G50">
-        <v>15.43</v>
+        <v>16.12</v>
       </c>
       <c r="H50">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="I50">
-        <v>29.56</v>
+        <v>27.42</v>
       </c>
       <c r="J50">
-        <v>20.7</v>
+        <v>21.815</v>
       </c>
       <c r="K50">
-        <v>-0.58</v>
+        <v>-1.49</v>
       </c>
       <c r="L50" t="s">
         <v>206</v>
@@ -2900,7 +2900,7 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
         <v>61</v>
@@ -2909,28 +2909,28 @@
         <v>153</v>
       </c>
       <c r="D51" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E51">
-        <v>22.85</v>
+        <v>27.47</v>
       </c>
       <c r="F51">
-        <v>5.08</v>
+        <v>2.82</v>
       </c>
       <c r="G51">
-        <v>17.14</v>
+        <v>20.6</v>
       </c>
       <c r="H51">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I51">
-        <v>21.94</v>
+        <v>28.84</v>
       </c>
       <c r="J51">
-        <v>23.025</v>
+        <v>27.935</v>
       </c>
       <c r="K51">
-        <v>-0.76</v>
+        <v>-1.66</v>
       </c>
       <c r="L51" t="s">
         <v>206</v>
@@ -2938,7 +2938,7 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
@@ -2947,28 +2947,28 @@
         <v>154</v>
       </c>
       <c r="D52" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E52">
-        <v>26.65</v>
+        <v>31.45</v>
       </c>
       <c r="F52">
-        <v>4.67</v>
+        <v>2.08</v>
       </c>
       <c r="G52">
-        <v>19.99</v>
+        <v>23.59</v>
       </c>
       <c r="H52">
-        <v>0.98</v>
+        <v>0.12</v>
       </c>
       <c r="I52">
-        <v>24.6</v>
+        <v>28.35</v>
       </c>
       <c r="J52">
-        <v>27.04</v>
+        <v>32.135</v>
       </c>
       <c r="K52">
-        <v>-1.44</v>
+        <v>-2.13</v>
       </c>
       <c r="L52" t="s">
         <v>206</v>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B53" t="s">
         <v>63</v>
@@ -2985,28 +2985,28 @@
         <v>155</v>
       </c>
       <c r="D53" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E53">
-        <v>29.11</v>
+        <v>24.02</v>
       </c>
       <c r="F53">
-        <v>5.11</v>
+        <v>2.48</v>
       </c>
       <c r="G53">
-        <v>21.83</v>
+        <v>18.02</v>
       </c>
       <c r="H53">
-        <v>0.14</v>
+        <v>1.66</v>
       </c>
       <c r="I53">
-        <v>29.36</v>
+        <v>23.02</v>
       </c>
       <c r="J53">
-        <v>29.64</v>
+        <v>24.67</v>
       </c>
       <c r="K53">
-        <v>-1.79</v>
+        <v>-2.63</v>
       </c>
       <c r="L53" t="s">
         <v>206</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
         <v>64</v>
@@ -3023,28 +3023,28 @@
         <v>156</v>
       </c>
       <c r="D54" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E54">
-        <v>28.95</v>
+        <v>23.74</v>
       </c>
       <c r="F54">
-        <v>2.36</v>
+        <v>5.39</v>
       </c>
       <c r="G54">
-        <v>21.71</v>
+        <v>17.8</v>
       </c>
       <c r="H54">
-        <v>1.19</v>
+        <v>0.6</v>
       </c>
       <c r="I54">
-        <v>24.52</v>
+        <v>23.1</v>
       </c>
       <c r="J54">
-        <v>29.64</v>
+        <v>24.415</v>
       </c>
       <c r="K54">
-        <v>-2.33</v>
+        <v>-2.76</v>
       </c>
       <c r="L54" t="s">
         <v>206</v>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
         <v>65</v>
@@ -3061,28 +3061,28 @@
         <v>157</v>
       </c>
       <c r="D55" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E55">
-        <v>26.4</v>
+        <v>28.99</v>
       </c>
       <c r="F55">
-        <v>5.79</v>
+        <v>3.27</v>
       </c>
       <c r="G55">
-        <v>19.8</v>
+        <v>21.74</v>
       </c>
       <c r="H55">
-        <v>0.36</v>
+        <v>1.97</v>
       </c>
       <c r="I55">
-        <v>26.16</v>
+        <v>28.99</v>
       </c>
       <c r="J55">
-        <v>27.04</v>
+        <v>29.825</v>
       </c>
       <c r="K55">
-        <v>-2.37</v>
+        <v>-2.8</v>
       </c>
       <c r="L55" t="s">
         <v>206</v>
@@ -3099,28 +3099,28 @@
         <v>158</v>
       </c>
       <c r="D56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E56">
-        <v>25.15</v>
+        <v>23.67</v>
       </c>
       <c r="F56">
-        <v>3.91</v>
+        <v>4.37</v>
       </c>
       <c r="G56">
-        <v>18.86</v>
+        <v>17.75</v>
       </c>
       <c r="H56">
         <v>0.52</v>
       </c>
       <c r="I56">
-        <v>22.58</v>
+        <v>23.51</v>
       </c>
       <c r="J56">
-        <v>25.76</v>
+        <v>24.67</v>
       </c>
       <c r="K56">
-        <v>-2.37</v>
+        <v>-4.05</v>
       </c>
       <c r="L56" t="s">
         <v>206</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
@@ -3137,28 +3137,28 @@
         <v>159</v>
       </c>
       <c r="D57" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E57">
-        <v>20.03</v>
+        <v>26.78</v>
       </c>
       <c r="F57">
-        <v>2.65</v>
+        <v>3.59</v>
       </c>
       <c r="G57">
-        <v>15.02</v>
+        <v>20.08</v>
       </c>
       <c r="H57">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="I57">
-        <v>27.02</v>
+        <v>29.2</v>
       </c>
       <c r="J57">
-        <v>20.545</v>
+        <v>27.935</v>
       </c>
       <c r="K57">
-        <v>-2.51</v>
+        <v>-4.13</v>
       </c>
       <c r="L57" t="s">
         <v>206</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B58" t="s">
         <v>68</v>
@@ -3175,28 +3175,28 @@
         <v>160</v>
       </c>
       <c r="D58" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E58">
-        <v>19.67</v>
+        <v>26.72</v>
       </c>
       <c r="F58">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G58">
-        <v>14.75</v>
+        <v>20.04</v>
       </c>
       <c r="H58">
-        <v>0.4</v>
+        <v>0.14</v>
       </c>
       <c r="I58">
-        <v>26.6</v>
+        <v>23.67</v>
       </c>
       <c r="J58">
-        <v>20.545</v>
+        <v>27.935</v>
       </c>
       <c r="K58">
-        <v>-4.26</v>
+        <v>-4.35</v>
       </c>
       <c r="L58" t="s">
         <v>206</v>
@@ -3204,7 +3204,7 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B59" t="s">
         <v>69</v>
@@ -3213,28 +3213,28 @@
         <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E59">
-        <v>25.86</v>
+        <v>20.55</v>
       </c>
       <c r="F59">
-        <v>5.06</v>
+        <v>2.4</v>
       </c>
       <c r="G59">
-        <v>19.4</v>
+        <v>15.41</v>
       </c>
       <c r="H59">
-        <v>1.06</v>
+        <v>0.21</v>
       </c>
       <c r="I59">
-        <v>29.75</v>
+        <v>24.21</v>
       </c>
       <c r="J59">
-        <v>27.04</v>
+        <v>21.815</v>
       </c>
       <c r="K59">
-        <v>-4.36</v>
+        <v>-5.8</v>
       </c>
       <c r="L59" t="s">
         <v>206</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
         <v>70</v>
@@ -3251,28 +3251,28 @@
         <v>162</v>
       </c>
       <c r="D60" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E60">
-        <v>19.69</v>
+        <v>22.92</v>
       </c>
       <c r="F60">
-        <v>2.01</v>
+        <v>4.78</v>
       </c>
       <c r="G60">
-        <v>14.77</v>
+        <v>17.19</v>
       </c>
       <c r="H60">
-        <v>1.18</v>
+        <v>0.34</v>
       </c>
       <c r="I60">
-        <v>20.54</v>
+        <v>23.5</v>
       </c>
       <c r="J60">
-        <v>20.7</v>
+        <v>24.415</v>
       </c>
       <c r="K60">
-        <v>-4.88</v>
+        <v>-6.12</v>
       </c>
       <c r="L60" t="s">
         <v>206</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B61" t="s">
         <v>71</v>
@@ -3289,28 +3289,28 @@
         <v>163</v>
       </c>
       <c r="D61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E61">
-        <v>19.89</v>
+        <v>18.97</v>
       </c>
       <c r="F61">
-        <v>3.85</v>
+        <v>5.15</v>
       </c>
       <c r="G61">
-        <v>14.92</v>
+        <v>14.23</v>
       </c>
       <c r="H61">
-        <v>1.37</v>
+        <v>0.32</v>
       </c>
       <c r="I61">
-        <v>21.95</v>
+        <v>24.41</v>
       </c>
       <c r="J61">
-        <v>21.26</v>
+        <v>20.355</v>
       </c>
       <c r="K61">
-        <v>-6.44</v>
+        <v>-6.8</v>
       </c>
       <c r="L61" t="s">
         <v>206</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B62" t="s">
         <v>72</v>
@@ -3330,25 +3330,25 @@
         <v>196</v>
       </c>
       <c r="E62">
-        <v>19.06</v>
+        <v>18.56</v>
       </c>
       <c r="F62">
-        <v>4.44</v>
+        <v>5.24</v>
       </c>
       <c r="G62">
-        <v>14.29</v>
+        <v>13.92</v>
       </c>
       <c r="H62">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="I62">
-        <v>27.27</v>
+        <v>24.41</v>
       </c>
       <c r="J62">
-        <v>20.7</v>
+        <v>20.355</v>
       </c>
       <c r="K62">
-        <v>-7.92</v>
+        <v>-8.82</v>
       </c>
       <c r="L62" t="s">
         <v>206</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B63" t="s">
         <v>73</v>
@@ -3365,28 +3365,28 @@
         <v>165</v>
       </c>
       <c r="D63" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E63">
-        <v>18.61</v>
+        <v>18.54</v>
       </c>
       <c r="F63">
-        <v>5.39</v>
+        <v>4.98</v>
       </c>
       <c r="G63">
-        <v>13.96</v>
+        <v>13.9</v>
       </c>
       <c r="H63">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="I63">
-        <v>21.75</v>
+        <v>22.54</v>
       </c>
       <c r="J63">
-        <v>20.545</v>
+        <v>20.355</v>
       </c>
       <c r="K63">
-        <v>-9.42</v>
+        <v>-8.92</v>
       </c>
       <c r="L63" t="s">
         <v>206</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B64" t="s">
         <v>74</v>
@@ -3403,28 +3403,28 @@
         <v>166</v>
       </c>
       <c r="D64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E64">
-        <v>23.39</v>
+        <v>26.89</v>
       </c>
       <c r="F64">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
       <c r="G64">
-        <v>17.54</v>
+        <v>20.17</v>
       </c>
       <c r="H64">
-        <v>0.55</v>
+        <v>4.07</v>
       </c>
       <c r="I64">
-        <v>29.99</v>
+        <v>25.48</v>
       </c>
       <c r="J64">
-        <v>26.345</v>
+        <v>29.825</v>
       </c>
       <c r="K64">
-        <v>-11.22</v>
+        <v>-9.84</v>
       </c>
       <c r="L64" t="s">
         <v>206</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
@@ -3441,28 +3441,28 @@
         <v>167</v>
       </c>
       <c r="D65" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E65">
-        <v>18.21</v>
+        <v>25.08</v>
       </c>
       <c r="F65">
-        <v>3.11</v>
+        <v>5.77</v>
       </c>
       <c r="G65">
-        <v>13.66</v>
+        <v>18.81</v>
       </c>
       <c r="H65">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="I65">
-        <v>23.36</v>
+        <v>24.32</v>
       </c>
       <c r="J65">
-        <v>20.545</v>
+        <v>27.88</v>
       </c>
       <c r="K65">
-        <v>-11.37</v>
+        <v>-10.04</v>
       </c>
       <c r="L65" t="s">
         <v>206</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="B66" t="s">
         <v>76</v>
@@ -3479,28 +3479,28 @@
         <v>168</v>
       </c>
       <c r="D66" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E66">
-        <v>18.74</v>
+        <v>21.49</v>
       </c>
       <c r="F66">
-        <v>2.76</v>
+        <v>3.41</v>
       </c>
       <c r="G66">
-        <v>14.06</v>
+        <v>16.12</v>
       </c>
       <c r="H66">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="I66">
-        <v>24.97</v>
+        <v>26.9</v>
       </c>
       <c r="J66">
-        <v>21.26</v>
+        <v>24.415</v>
       </c>
       <c r="K66">
-        <v>-11.85</v>
+        <v>-11.98</v>
       </c>
       <c r="L66" t="s">
         <v>206</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
         <v>77</v>
@@ -3520,25 +3520,25 @@
         <v>202</v>
       </c>
       <c r="E67">
-        <v>23.08</v>
+        <v>26.25</v>
       </c>
       <c r="F67">
-        <v>2.72</v>
+        <v>5.61</v>
       </c>
       <c r="G67">
-        <v>17.31</v>
+        <v>19.69</v>
       </c>
       <c r="H67">
-        <v>0.27</v>
+        <v>0.95</v>
       </c>
       <c r="I67">
-        <v>24.56</v>
+        <v>25.94</v>
       </c>
       <c r="J67">
-        <v>26.345</v>
+        <v>30.1</v>
       </c>
       <c r="K67">
-        <v>-12.39</v>
+        <v>-12.79</v>
       </c>
       <c r="L67" t="s">
         <v>206</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B68" t="s">
         <v>78</v>
@@ -3555,28 +3555,28 @@
         <v>170</v>
       </c>
       <c r="D68" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E68">
-        <v>20.03</v>
+        <v>24.24</v>
       </c>
       <c r="F68">
-        <v>3.51</v>
+        <v>2.22</v>
       </c>
       <c r="G68">
-        <v>15.02</v>
+        <v>18.18</v>
       </c>
       <c r="H68">
-        <v>0.71</v>
+        <v>0.42</v>
       </c>
       <c r="I68">
-        <v>27.86</v>
+        <v>25.92</v>
       </c>
       <c r="J68">
-        <v>23.025</v>
+        <v>27.88</v>
       </c>
       <c r="K68">
-        <v>-13.01</v>
+        <v>-13.06</v>
       </c>
       <c r="L68" t="s">
         <v>206</v>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
         <v>79</v>
@@ -3593,28 +3593,28 @@
         <v>171</v>
       </c>
       <c r="D69" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E69">
-        <v>17.94</v>
+        <v>25.6</v>
       </c>
       <c r="F69">
-        <v>3.85</v>
+        <v>2.72</v>
       </c>
       <c r="G69">
-        <v>13.46</v>
+        <v>19.2</v>
       </c>
       <c r="H69">
-        <v>0.12</v>
+        <v>2.51</v>
       </c>
       <c r="I69">
-        <v>29.12</v>
+        <v>22.15</v>
       </c>
       <c r="J69">
-        <v>20.7</v>
+        <v>30.1</v>
       </c>
       <c r="K69">
-        <v>-13.33</v>
+        <v>-14.95</v>
       </c>
       <c r="L69" t="s">
         <v>206</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B70" t="s">
         <v>80</v>
@@ -3631,28 +3631,28 @@
         <v>172</v>
       </c>
       <c r="D70" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E70">
-        <v>19.78</v>
+        <v>25.26</v>
       </c>
       <c r="F70">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="G70">
-        <v>14.84</v>
+        <v>18.94</v>
       </c>
       <c r="H70">
-        <v>0.49</v>
+        <v>0.36</v>
       </c>
       <c r="I70">
-        <v>24.54</v>
+        <v>26.1</v>
       </c>
       <c r="J70">
-        <v>23.45</v>
+        <v>29.825</v>
       </c>
       <c r="K70">
-        <v>-15.65</v>
+        <v>-15.31</v>
       </c>
       <c r="L70" t="s">
         <v>206</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B71" t="s">
         <v>81</v>
@@ -3669,28 +3669,28 @@
         <v>173</v>
       </c>
       <c r="D71" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E71">
-        <v>24.9</v>
+        <v>25.37</v>
       </c>
       <c r="F71">
-        <v>3.42</v>
+        <v>3.87</v>
       </c>
       <c r="G71">
-        <v>18.67</v>
+        <v>19.03</v>
       </c>
       <c r="H71">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="I71">
-        <v>24.42</v>
+        <v>26.52</v>
       </c>
       <c r="J71">
-        <v>29.64</v>
+        <v>30.1</v>
       </c>
       <c r="K71">
-        <v>-15.99</v>
+        <v>-15.71</v>
       </c>
       <c r="L71" t="s">
         <v>206</v>
@@ -3707,28 +3707,28 @@
         <v>174</v>
       </c>
       <c r="D72" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E72">
-        <v>17.07</v>
+        <v>25.1</v>
       </c>
       <c r="F72">
-        <v>2.58</v>
+        <v>4.03</v>
       </c>
       <c r="G72">
-        <v>12.8</v>
+        <v>18.83</v>
       </c>
       <c r="H72">
         <v>0.79</v>
       </c>
       <c r="I72">
-        <v>23.52</v>
+        <v>25.96</v>
       </c>
       <c r="J72">
-        <v>21.26</v>
+        <v>30.1</v>
       </c>
       <c r="K72">
-        <v>-19.71</v>
+        <v>-16.61</v>
       </c>
       <c r="L72" t="s">
         <v>206</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="B73" t="s">
         <v>83</v>
@@ -3745,28 +3745,28 @@
         <v>175</v>
       </c>
       <c r="D73" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E73">
-        <v>16.47</v>
+        <v>23.01</v>
       </c>
       <c r="F73">
-        <v>5.05</v>
+        <v>2.1</v>
       </c>
       <c r="G73">
-        <v>12.35</v>
+        <v>17.26</v>
       </c>
       <c r="H73">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="I73">
-        <v>20.31</v>
+        <v>29.1</v>
       </c>
       <c r="J73">
-        <v>20.545</v>
+        <v>27.88</v>
       </c>
       <c r="K73">
-        <v>-19.83</v>
+        <v>-17.47</v>
       </c>
       <c r="L73" t="s">
         <v>206</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="B74" t="s">
         <v>84</v>
@@ -3783,28 +3783,28 @@
         <v>176</v>
       </c>
       <c r="D74" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E74">
-        <v>20.76</v>
+        <v>16.79</v>
       </c>
       <c r="F74">
-        <v>2.71</v>
+        <v>2.27</v>
       </c>
       <c r="G74">
-        <v>15.57</v>
+        <v>12.59</v>
       </c>
       <c r="H74">
-        <v>0.98</v>
+        <v>0.32</v>
       </c>
       <c r="I74">
-        <v>25.61</v>
+        <v>23.2</v>
       </c>
       <c r="J74">
-        <v>26.345</v>
+        <v>20.355</v>
       </c>
       <c r="K74">
-        <v>-21.2</v>
+        <v>-17.51</v>
       </c>
       <c r="L74" t="s">
         <v>206</v>
@@ -3812,7 +3812,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
         <v>85</v>
@@ -3824,25 +3824,25 @@
         <v>202</v>
       </c>
       <c r="E75">
-        <v>20.72</v>
+        <v>24.7</v>
       </c>
       <c r="F75">
-        <v>4.85</v>
+        <v>5.75</v>
       </c>
       <c r="G75">
-        <v>15.54</v>
+        <v>18.52</v>
       </c>
       <c r="H75">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="I75">
-        <v>21.71</v>
+        <v>23.35</v>
       </c>
       <c r="J75">
-        <v>26.345</v>
+        <v>30.1</v>
       </c>
       <c r="K75">
-        <v>-21.35</v>
+        <v>-17.94</v>
       </c>
       <c r="L75" t="s">
         <v>206</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
         <v>86</v>
@@ -3859,28 +3859,28 @@
         <v>178</v>
       </c>
       <c r="D76" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E76">
-        <v>18.13</v>
+        <v>17.9</v>
       </c>
       <c r="F76">
-        <v>5.69</v>
+        <v>4.79</v>
       </c>
       <c r="G76">
-        <v>13.6</v>
+        <v>13.42</v>
       </c>
       <c r="H76">
-        <v>0.31</v>
+        <v>0.54</v>
       </c>
       <c r="I76">
-        <v>28.68</v>
+        <v>19.3</v>
       </c>
       <c r="J76">
-        <v>23.45</v>
+        <v>21.815</v>
       </c>
       <c r="K76">
-        <v>-22.69</v>
+        <v>-17.95</v>
       </c>
       <c r="L76" t="s">
         <v>206</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
         <v>87</v>
@@ -3900,25 +3900,25 @@
         <v>197</v>
       </c>
       <c r="E77">
-        <v>16.03</v>
+        <v>17.79</v>
       </c>
       <c r="F77">
-        <v>3.21</v>
+        <v>4.68</v>
       </c>
       <c r="G77">
-        <v>12.02</v>
+        <v>13.34</v>
       </c>
       <c r="H77">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="I77">
-        <v>23.68</v>
+        <v>22.92</v>
       </c>
       <c r="J77">
-        <v>21.26</v>
+        <v>21.815</v>
       </c>
       <c r="K77">
-        <v>-24.6</v>
+        <v>-18.45</v>
       </c>
       <c r="L77" t="s">
         <v>206</v>
@@ -3926,7 +3926,7 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B78" t="s">
         <v>88</v>
@@ -3935,28 +3935,28 @@
         <v>180</v>
       </c>
       <c r="D78" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E78">
-        <v>17.11</v>
+        <v>24.79</v>
       </c>
       <c r="F78">
-        <v>3.41</v>
+        <v>3.74</v>
       </c>
       <c r="G78">
-        <v>12.83</v>
+        <v>18.59</v>
       </c>
       <c r="H78">
         <v>0.36</v>
       </c>
       <c r="I78">
-        <v>23.68</v>
+        <v>22.66</v>
       </c>
       <c r="J78">
-        <v>23.025</v>
+        <v>32.135</v>
       </c>
       <c r="K78">
-        <v>-25.69</v>
+        <v>-22.86</v>
       </c>
       <c r="L78" t="s">
         <v>206</v>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
         <v>89</v>
@@ -3973,28 +3973,28 @@
         <v>181</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E79">
-        <v>19.48</v>
+        <v>19.02</v>
       </c>
       <c r="F79">
-        <v>5.93</v>
+        <v>3.42</v>
       </c>
       <c r="G79">
-        <v>14.61</v>
+        <v>14.26</v>
       </c>
       <c r="H79">
-        <v>0.67</v>
+        <v>0.32</v>
       </c>
       <c r="I79">
-        <v>21.74</v>
+        <v>22.49</v>
       </c>
       <c r="J79">
-        <v>26.345</v>
+        <v>24.67</v>
       </c>
       <c r="K79">
-        <v>-26.06</v>
+        <v>-22.9</v>
       </c>
       <c r="L79" t="s">
         <v>206</v>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B80" t="s">
         <v>90</v>
@@ -4011,28 +4011,28 @@
         <v>182</v>
       </c>
       <c r="D80" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E80">
-        <v>16.79</v>
+        <v>16.71</v>
       </c>
       <c r="F80">
-        <v>5.21</v>
+        <v>4.17</v>
       </c>
       <c r="G80">
-        <v>12.59</v>
+        <v>12.53</v>
       </c>
       <c r="H80">
-        <v>0.29</v>
+        <v>0.7</v>
       </c>
       <c r="I80">
-        <v>21.18</v>
+        <v>28.52</v>
       </c>
       <c r="J80">
-        <v>23.025</v>
+        <v>21.815</v>
       </c>
       <c r="K80">
-        <v>-27.08</v>
+        <v>-23.4</v>
       </c>
       <c r="L80" t="s">
         <v>206</v>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
         <v>91</v>
@@ -4049,28 +4049,28 @@
         <v>183</v>
       </c>
       <c r="D81" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E81">
-        <v>16.69</v>
+        <v>23.85</v>
       </c>
       <c r="F81">
-        <v>4.49</v>
+        <v>3.2</v>
       </c>
       <c r="G81">
-        <v>12.52</v>
+        <v>17.89</v>
       </c>
       <c r="H81">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="I81">
-        <v>21.82</v>
+        <v>23.33</v>
       </c>
       <c r="J81">
-        <v>23.025</v>
+        <v>32.135</v>
       </c>
       <c r="K81">
-        <v>-27.51</v>
+        <v>-25.78</v>
       </c>
       <c r="L81" t="s">
         <v>206</v>
@@ -4078,7 +4078,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B82" t="s">
         <v>92</v>
@@ -4087,28 +4087,28 @@
         <v>184</v>
       </c>
       <c r="D82" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E82">
-        <v>21.44</v>
+        <v>18.01</v>
       </c>
       <c r="F82">
-        <v>4.27</v>
+        <v>5.88</v>
       </c>
       <c r="G82">
-        <v>16.08</v>
+        <v>13.51</v>
       </c>
       <c r="H82">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="I82">
-        <v>26.81</v>
+        <v>28.12</v>
       </c>
       <c r="J82">
-        <v>29.64</v>
+        <v>24.415</v>
       </c>
       <c r="K82">
-        <v>-27.67</v>
+        <v>-26.23</v>
       </c>
       <c r="L82" t="s">
         <v>206</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B83" t="s">
         <v>93</v>
@@ -4125,28 +4125,28 @@
         <v>185</v>
       </c>
       <c r="D83" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E83">
-        <v>15.05</v>
+        <v>20.38</v>
       </c>
       <c r="F83">
-        <v>2.07</v>
+        <v>5.92</v>
       </c>
       <c r="G83">
-        <v>11.29</v>
+        <v>15.28</v>
       </c>
       <c r="H83">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="I83">
-        <v>23.34</v>
+        <v>20.74</v>
       </c>
       <c r="J83">
-        <v>21.26</v>
+        <v>27.88</v>
       </c>
       <c r="K83">
-        <v>-29.21</v>
+        <v>-26.9</v>
       </c>
       <c r="L83" t="s">
         <v>206</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B84" t="s">
         <v>94</v>
@@ -4163,36 +4163,36 @@
         <v>186</v>
       </c>
       <c r="D84" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E84">
-        <v>18.01</v>
+        <v>23.47</v>
       </c>
       <c r="F84">
-        <v>4.15</v>
+        <v>2.28</v>
       </c>
       <c r="G84">
-        <v>13.51</v>
+        <v>17.6</v>
       </c>
       <c r="H84">
-        <v>1.28</v>
+        <v>0.52</v>
       </c>
       <c r="I84">
-        <v>22.6</v>
+        <v>24.76</v>
       </c>
       <c r="J84">
-        <v>25.76</v>
+        <v>32.135</v>
       </c>
       <c r="K84">
-        <v>-30.09</v>
+        <v>-26.96</v>
       </c>
       <c r="L84" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="B85" t="s">
         <v>95</v>
@@ -4201,36 +4201,36 @@
         <v>187</v>
       </c>
       <c r="D85" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E85">
-        <v>17.81</v>
+        <v>17.83</v>
       </c>
       <c r="F85">
-        <v>2.64</v>
+        <v>4.91</v>
       </c>
       <c r="G85">
-        <v>13.36</v>
+        <v>13.37</v>
       </c>
       <c r="H85">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="I85">
-        <v>22.74</v>
+        <v>28.26</v>
       </c>
       <c r="J85">
-        <v>25.76</v>
+        <v>24.415</v>
       </c>
       <c r="K85">
-        <v>-30.86</v>
+        <v>-26.97</v>
       </c>
       <c r="L85" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B86" t="s">
         <v>96</v>
@@ -4239,36 +4239,36 @@
         <v>188</v>
       </c>
       <c r="D86" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E86">
-        <v>17.76</v>
+        <v>17.28</v>
       </c>
       <c r="F86">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="G86">
-        <v>13.32</v>
+        <v>12.96</v>
       </c>
       <c r="H86">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="I86">
-        <v>25.63</v>
+        <v>22.62</v>
       </c>
       <c r="J86">
-        <v>25.76</v>
+        <v>24.67</v>
       </c>
       <c r="K86">
-        <v>-31.06</v>
+        <v>-29.96</v>
       </c>
       <c r="L86" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="B87" t="s">
         <v>97</v>
@@ -4277,28 +4277,28 @@
         <v>189</v>
       </c>
       <c r="D87" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E87">
-        <v>17.92</v>
+        <v>22.23</v>
       </c>
       <c r="F87">
-        <v>3.52</v>
+        <v>5.08</v>
       </c>
       <c r="G87">
-        <v>13.44</v>
+        <v>16.67</v>
       </c>
       <c r="H87">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="I87">
-        <v>26.87</v>
+        <v>24.42</v>
       </c>
       <c r="J87">
-        <v>27.04</v>
+        <v>32.135</v>
       </c>
       <c r="K87">
-        <v>-33.73</v>
+        <v>-30.82</v>
       </c>
       <c r="L87" t="s">
         <v>207</v>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="B88" t="s">
         <v>98</v>
@@ -4315,28 +4315,28 @@
         <v>190</v>
       </c>
       <c r="D88" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E88">
-        <v>19.6</v>
+        <v>18.84</v>
       </c>
       <c r="F88">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="G88">
-        <v>14.7</v>
+        <v>14.13</v>
       </c>
       <c r="H88">
-        <v>2.15</v>
+        <v>0.42</v>
       </c>
       <c r="I88">
-        <v>25.21</v>
+        <v>29.94</v>
       </c>
       <c r="J88">
-        <v>29.64</v>
+        <v>27.935</v>
       </c>
       <c r="K88">
-        <v>-33.87</v>
+        <v>-32.56</v>
       </c>
       <c r="L88" t="s">
         <v>207</v>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B89" t="s">
         <v>99</v>
@@ -4353,28 +4353,28 @@
         <v>191</v>
       </c>
       <c r="D89" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E89">
-        <v>15.4</v>
+        <v>16.05</v>
       </c>
       <c r="F89">
-        <v>5.73</v>
+        <v>3.97</v>
       </c>
       <c r="G89">
-        <v>11.55</v>
+        <v>12.04</v>
       </c>
       <c r="H89">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I89">
-        <v>24.3</v>
+        <v>26.73</v>
       </c>
       <c r="J89">
-        <v>23.45</v>
+        <v>24.67</v>
       </c>
       <c r="K89">
-        <v>-34.33</v>
+        <v>-34.94</v>
       </c>
       <c r="L89" t="s">
         <v>207</v>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B90" t="s">
         <v>100</v>
@@ -4391,28 +4391,28 @@
         <v>192</v>
       </c>
       <c r="D90" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E90">
-        <v>15.39</v>
+        <v>18.45</v>
       </c>
       <c r="F90">
-        <v>4.64</v>
+        <v>2.26</v>
       </c>
       <c r="G90">
-        <v>11.54</v>
+        <v>13.84</v>
       </c>
       <c r="H90">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="I90">
-        <v>23.9</v>
+        <v>23.73</v>
       </c>
       <c r="J90">
-        <v>23.45</v>
+        <v>29.825</v>
       </c>
       <c r="K90">
-        <v>-34.37</v>
+        <v>-38.14</v>
       </c>
       <c r="L90" t="s">
         <v>207</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B91" t="s">
         <v>101</v>
@@ -4429,28 +4429,28 @@
         <v>193</v>
       </c>
       <c r="D91" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E91">
-        <v>15.12</v>
+        <v>17.17</v>
       </c>
       <c r="F91">
-        <v>4.41</v>
+        <v>2.79</v>
       </c>
       <c r="G91">
-        <v>11.34</v>
+        <v>12.88</v>
       </c>
       <c r="H91">
-        <v>0.34</v>
+        <v>1.19</v>
       </c>
       <c r="I91">
-        <v>23.46</v>
+        <v>27.24</v>
       </c>
       <c r="J91">
-        <v>23.45</v>
+        <v>27.935</v>
       </c>
       <c r="K91">
-        <v>-35.52</v>
+        <v>-38.54</v>
       </c>
       <c r="L91" t="s">
         <v>207</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B92" t="s">
         <v>102</v>
@@ -4467,28 +4467,28 @@
         <v>194</v>
       </c>
       <c r="D92" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E92">
-        <v>16.02</v>
+        <v>17.69</v>
       </c>
       <c r="F92">
-        <v>4.65</v>
+        <v>2.04</v>
       </c>
       <c r="G92">
-        <v>12.02</v>
+        <v>13.27</v>
       </c>
       <c r="H92">
-        <v>0.37</v>
+        <v>0.54</v>
       </c>
       <c r="I92">
-        <v>21.17</v>
+        <v>20.88</v>
       </c>
       <c r="J92">
-        <v>25.76</v>
+        <v>29.825</v>
       </c>
       <c r="K92">
-        <v>-37.81</v>
+        <v>-40.69</v>
       </c>
       <c r="L92" t="s">
         <v>207</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="B93" t="s">
         <v>103</v>
@@ -4508,22 +4508,22 @@
         <v>201</v>
       </c>
       <c r="E93">
-        <v>15.47</v>
+        <v>15.95</v>
       </c>
       <c r="F93">
-        <v>2.79</v>
+        <v>5.46</v>
       </c>
       <c r="G93">
-        <v>11.6</v>
+        <v>11.96</v>
       </c>
       <c r="H93">
-        <v>0.52</v>
+        <v>0.96</v>
       </c>
       <c r="I93">
-        <v>29.51</v>
+        <v>23.94</v>
       </c>
       <c r="J93">
-        <v>27.04</v>
+        <v>27.88</v>
       </c>
       <c r="K93">
         <v>-42.79</v>
